--- a/assets/ESR Formations-French.xlsx
+++ b/assets/ESR Formations-French.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{5B5579AA-790E-4F9F-96D2-3CC922622812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB103DB9-DF36-4D6F-BCD4-7CF4822AE905}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{5B5579AA-790E-4F9F-96D2-3CC922622812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EAC3F1A-BE30-48A3-BA61-D81F9255B9D5}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="555" windowWidth="21285" windowHeight="14700" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="1950" yWindow="780" windowWidth="21285" windowHeight="14700" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="67">
   <si>
     <t>Formation</t>
   </si>
@@ -112,142 +112,172 @@
     <t>Reinforcements</t>
   </si>
   <si>
-    <t>Avant Garde</t>
-  </si>
-  <si>
-    <t>Mixed</t>
-  </si>
-  <si>
-    <t>Genzer Bataillone</t>
-  </si>
-  <si>
-    <t>Chevaulégèr Sqn Grps</t>
-  </si>
-  <si>
-    <t>Würst Artillerie-Batterie</t>
-  </si>
-  <si>
-    <t>Infanterie Division</t>
-  </si>
-  <si>
-    <t>Big Battalions*</t>
-  </si>
-  <si>
-    <t>Infanterie Bataillone</t>
-  </si>
-  <si>
-    <t>Brigade-Batterie</t>
-  </si>
-  <si>
-    <t>Reservieren Division</t>
-  </si>
-  <si>
-    <t>Enthusiastic</t>
-  </si>
-  <si>
-    <t>Grenadier Bataillone</t>
-  </si>
-  <si>
-    <t>Leichte Kavallerie Brigade</t>
-  </si>
-  <si>
-    <t>Husaren Sqn Grps</t>
-  </si>
-  <si>
-    <t>Kavallerie Brigade/Division</t>
-  </si>
-  <si>
-    <t>Chevauleger Sqn Grps</t>
-  </si>
-  <si>
-    <t>Dragoner Sqn Grps</t>
-  </si>
-  <si>
-    <t>Würst Artillerie</t>
-  </si>
-  <si>
-    <t>6**</t>
-  </si>
-  <si>
-    <t>**Any mix</t>
-  </si>
-  <si>
-    <t>Kürassier Division</t>
-  </si>
-  <si>
-    <t>Kürassiere Sqn Grps</t>
-  </si>
-  <si>
-    <t>Korps Reservieren</t>
-  </si>
-  <si>
-    <t>Position-Batterie</t>
-  </si>
-  <si>
-    <t>Leitche Artillerie</t>
-  </si>
-  <si>
     <t>Unit</t>
   </si>
   <si>
-    <t>Grenzer</t>
-  </si>
-  <si>
     <t>Infantry Battalion</t>
   </si>
   <si>
-    <t>Jägere</t>
-  </si>
-  <si>
-    <t>Infanterie</t>
-  </si>
-  <si>
-    <t>Grenadiere</t>
-  </si>
-  <si>
-    <t>Landwehr</t>
-  </si>
-  <si>
-    <t>Pioneere</t>
-  </si>
-  <si>
     <t>Infantry Company (Asset)</t>
   </si>
   <si>
     <t>Sapeurs</t>
   </si>
   <si>
-    <t>Kürassiere</t>
-  </si>
-  <si>
     <t>Cavalry Squadron Group</t>
   </si>
   <si>
-    <t>Husaren</t>
-  </si>
-  <si>
-    <t>Ulanen</t>
-  </si>
-  <si>
-    <t>Position-Batterien</t>
-  </si>
-  <si>
     <t>Artillery Battery (Asset)</t>
   </si>
   <si>
-    <t>Brigade-Batterien</t>
-  </si>
-  <si>
     <t>Formation\Unit</t>
   </si>
   <si>
+    <t>Division d’Infanterie</t>
+  </si>
+  <si>
+    <t>Infanterie Légère Bataillons*</t>
+  </si>
+  <si>
+    <t>Infanterie de Ligne Bataillons</t>
+  </si>
+  <si>
+    <t>Artillerie à Pied Batterie</t>
+  </si>
+  <si>
+    <t>*May not exceed 1/3 of the Infanterie Bataillons</t>
+  </si>
+  <si>
+    <t>Brigade de Cavalerie Légère</t>
+  </si>
+  <si>
+    <t>Chasseurs à Cheval Squadron Groups</t>
+  </si>
+  <si>
+    <t>Division de Cavalerie Légère</t>
+  </si>
+  <si>
+    <t>Hussard Squadron Groups</t>
+  </si>
+  <si>
+    <t>Artillerie à Cheval Batterie</t>
+  </si>
+  <si>
+    <t>Division de Cavalerie/Dragons</t>
+  </si>
+  <si>
+    <t>Dragon Squadron Groups</t>
+  </si>
+  <si>
+    <t>Division de Grosse Cavalerie</t>
+  </si>
+  <si>
+    <t>Cuirassier Squadron Groups</t>
+  </si>
+  <si>
+    <t>Corps Réserve/Parc d’Artillerie</t>
+  </si>
+  <si>
+    <t>Réserve d’Artillerie Batterie</t>
+  </si>
+  <si>
+    <t>Sapeur Compagnie</t>
+  </si>
+  <si>
+    <t>1er &amp; 2eme Grenadiers à Pied de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>1er &amp; 2eme Chasseurs à Pied de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>3eme (Dutch) Grenadiers à Pied de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Fusilier-Grenadiers à Pied de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Fusilier-Chasseurs à Pied de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Tirailleurs de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Voltigeurs de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Grenadiers à Cheval de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Gendarmes d’élite de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Dragons de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Chasseurs à Cheval de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Mameluks de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Chevau-Légèr-Lanciers Polonais de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Chevau-Légèr-Lanciers Hollandais de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Réserve Artillerie de la Vieille Garde</t>
+  </si>
+  <si>
+    <t>Artillerie à Cheval de la Vieille Garde</t>
+  </si>
+  <si>
+    <t>Artillerie à Pied de la Vieille Garde</t>
+  </si>
+  <si>
+    <t>Artillerie à Pied de la Jeune Garde</t>
+  </si>
+  <si>
+    <t>Infanterie Légère</t>
+  </si>
+  <si>
+    <t>Infanterie de Ligne</t>
+  </si>
+  <si>
+    <t>Carabiniers à Cheval</t>
+  </si>
+  <si>
+    <t>Cuirassiers</t>
+  </si>
+  <si>
+    <t>Dragons</t>
+  </si>
+  <si>
+    <t>Chevau-Légèr-Lanciers</t>
+  </si>
+  <si>
+    <t>Chasseurs à Cheval</t>
+  </si>
+  <si>
+    <t>Hussards</t>
+  </si>
+  <si>
+    <t>12-pdr Réserve d’Artillerie</t>
+  </si>
+  <si>
+    <t>6-pdr Artillerie à Pied</t>
+  </si>
+  <si>
+    <t>6-pdr Artillerie à Cheval</t>
+  </si>
+  <si>
+    <t>Division d’Infanterie de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>Brigade de Cavalerie de la Garde Impériale</t>
+  </si>
+  <si>
     <t>x</t>
-  </si>
-  <si>
-    <t>Chevaulegers</t>
-  </si>
-  <si>
-    <t>Dragoner</t>
   </si>
 </sst>
 </file>
@@ -312,7 +342,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -350,11 +380,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF404040"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -392,6 +431,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -407,6 +449,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -726,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210EA6EE-836D-4B1C-9447-4891875C4300}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="10" width="25.5703125" style="10" customWidth="1"/>
@@ -752,358 +798,482 @@
         <v>5</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C2" s="11"/>
       <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3">
-        <v>4</v>
-      </c>
-      <c r="F2" s="11"/>
+        <v>19</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F3" s="11"/>
       <c r="I3" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
+      <c r="A4" s="2"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
       </c>
       <c r="F4" s="11"/>
       <c r="I4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="85.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="I5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="11"/>
+      <c r="I6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="I7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="J7" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="I8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="I9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="5">
+        <v>9</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="I10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="I11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="3">
+        <v>9</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="I12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="I13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="I14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="I15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="I16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="I17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="12" t="s">
+    </row>
+    <row r="18" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5">
-        <v>9</v>
-      </c>
-      <c r="F5" s="12"/>
-      <c r="I5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="I6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="I18" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="I20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="I7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="5">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="I8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="I10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="11"/>
-      <c r="I11" s="8" t="s">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="5">
-        <v>6</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="I12" s="8" t="s">
+      <c r="J24" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I25" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="I13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="I14" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3</v>
-      </c>
-      <c r="F15" s="11"/>
-      <c r="I15" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="3">
-        <v>2</v>
-      </c>
-      <c r="F16" s="11"/>
-      <c r="I16" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="9:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>51</v>
+      <c r="J25" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I26" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I27" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I29" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I31" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I32" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="F14:F16"/>
+  <mergeCells count="19">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="C14:C17"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="F14:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1111,16 +1281,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A52F401-E5BC-41DA-8596-65382229DEB1}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="24.85546875" customWidth="1"/>
     <col min="4" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="10" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>1</v>
@@ -1129,146 +1299,170 @@
         <v>2</v>
       </c>
       <c r="D1" s="10" t="str" cm="1">
-        <f t="array" ref="D1:S1">TRANSPOSE( BaselineFormations!I3:I18 )</f>
-        <v>Grenzer</v>
+        <f t="array" ref="D1:AG1">TRANSPOSE( BaselineFormations!I3:I32 )</f>
+        <v>1er &amp; 2eme Grenadiers à Pied de la Garde Impériale</v>
       </c>
       <c r="E1" s="10" t="str">
-        <v>Jägere</v>
+        <v>1er &amp; 2eme Chasseurs à Pied de la Garde Impériale</v>
       </c>
       <c r="F1" s="10" t="str">
-        <v>Infanterie</v>
+        <v>3eme (Dutch) Grenadiers à Pied de la Garde Impériale</v>
       </c>
       <c r="G1" s="10" t="str">
-        <v>Grenadiere</v>
+        <v>Fusilier-Grenadiers à Pied de la Garde Impériale</v>
       </c>
       <c r="H1" s="10" t="str">
-        <v>Landwehr</v>
+        <v>Fusilier-Chasseurs à Pied de la Garde Impériale</v>
       </c>
       <c r="I1" s="10" t="str">
-        <v>Pioneere</v>
+        <v>Tirailleurs de la Garde Impériale</v>
       </c>
       <c r="J1" s="10" t="str">
+        <v>Voltigeurs de la Garde Impériale</v>
+      </c>
+      <c r="K1" s="10" t="str">
+        <v>Grenadiers à Cheval de la Garde Impériale</v>
+      </c>
+      <c r="L1" s="10" t="str">
+        <v>Gendarmes d’élite de la Garde Impériale</v>
+      </c>
+      <c r="M1" s="10" t="str">
+        <v>Dragons de la Garde Impériale</v>
+      </c>
+      <c r="N1" s="10" t="str">
+        <v>Chasseurs à Cheval de la Garde Impériale</v>
+      </c>
+      <c r="O1" s="10" t="str">
+        <v>Mameluks de la Garde Impériale</v>
+      </c>
+      <c r="P1" s="10" t="str">
+        <v>Chevau-Légèr-Lanciers Polonais de la Garde Impériale</v>
+      </c>
+      <c r="Q1" s="10" t="str">
+        <v>Chevau-Légèr-Lanciers Hollandais de la Garde Impériale</v>
+      </c>
+      <c r="R1" s="10" t="str">
+        <v>Réserve Artillerie de la Vieille Garde</v>
+      </c>
+      <c r="S1" s="10" t="str">
+        <v>Artillerie à Cheval de la Vieille Garde</v>
+      </c>
+      <c r="T1" s="10" t="str">
+        <v>Artillerie à Pied de la Vieille Garde</v>
+      </c>
+      <c r="U1" s="10" t="str">
+        <v>Artillerie à Pied de la Jeune Garde</v>
+      </c>
+      <c r="V1" s="10" t="str">
+        <v>Infanterie Légère</v>
+      </c>
+      <c r="W1" s="10" t="str">
+        <v>Infanterie de Ligne</v>
+      </c>
+      <c r="X1" s="10" t="str">
         <v>Sapeurs</v>
       </c>
-      <c r="K1" s="10" t="str">
-        <v>Kürassiere</v>
-      </c>
-      <c r="L1" s="10" t="str">
-        <v>Chevaulegers</v>
-      </c>
-      <c r="M1" s="10" t="str">
-        <v>Dragoner</v>
-      </c>
-      <c r="N1" s="10" t="str">
-        <v>Husaren</v>
-      </c>
-      <c r="O1" s="10" t="str">
-        <v>Ulanen</v>
-      </c>
-      <c r="P1" s="10" t="str">
-        <v>Position-Batterien</v>
-      </c>
-      <c r="Q1" s="10" t="str">
-        <v>Brigade-Batterien</v>
-      </c>
-      <c r="R1" s="10" t="str">
-        <v>Leitche Artillerie</v>
-      </c>
-      <c r="S1" s="10" t="str">
-        <v>Würst Artillerie</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Y1" s="10" t="str">
+        <v>Carabiniers à Cheval</v>
+      </c>
+      <c r="Z1" s="10" t="str">
+        <v>Cuirassiers</v>
+      </c>
+      <c r="AA1" s="10" t="str">
+        <v>Dragons</v>
+      </c>
+      <c r="AB1" s="10" t="str">
+        <v>Chevau-Légèr-Lanciers</v>
+      </c>
+      <c r="AC1" s="10" t="str">
+        <v>Chasseurs à Cheval</v>
+      </c>
+      <c r="AD1" s="10" t="str">
+        <v>Hussards</v>
+      </c>
+      <c r="AE1" s="10" t="str">
+        <v>12-pdr Réserve d’Artillerie</v>
+      </c>
+      <c r="AF1" s="10" t="str">
+        <v>6-pdr Artillerie à Pied</v>
+      </c>
+      <c r="AG1" s="10" t="str">
+        <v>6-pdr Artillerie à Cheval</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C8">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
-        <v>Avant Garde</v>
+        <f t="array" ref="A2:C9">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
+        <v>Division d’Infanterie</v>
       </c>
       <c r="B2" t="str">
-        <v>Mixed</v>
+        <v/>
       </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <v>Brigade de Cavalerie Légère</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Cavalry</v>
+      </c>
+      <c r="C3" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="D2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>Infanterie Division</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Infantry</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Big Battalions*</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3" t="s">
-        <v>54</v>
-      </c>
-      <c r="P3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AC3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>Reservieren Division</v>
+        <v>Division de Cavalerie Légère</v>
       </c>
       <c r="B4" t="str">
-        <v>Infantry</v>
+        <v>Cavalry</v>
       </c>
       <c r="C4" t="str">
-        <v>Enthusiastic</v>
-      </c>
-      <c r="G4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P4" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+        <v>Rapid Deployment</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>Leichte Kavallerie Brigade</v>
+        <v>Division de Cavalerie/Dragons</v>
       </c>
       <c r="B5" t="str">
         <v>Cavalry</v>
@@ -1276,22 +1470,16 @@
       <c r="C5" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="L5" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" t="s">
-        <v>54</v>
-      </c>
-      <c r="S5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>Kavallerie Brigade/Division</v>
+        <v>Division de Grosse Cavalerie</v>
       </c>
       <c r="B6" t="str">
         <v>Cavalry</v>
@@ -1299,51 +1487,116 @@
       <c r="C6" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="L6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Y6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>Kürassier Division</v>
+        <v>Corps Réserve/Parc d’Artillerie</v>
       </c>
       <c r="B7" t="str">
+        <v>Artillery</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Reinforcements</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <v>Division d’Infanterie de la Garde Impériale</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Infantry</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" t="s">
+        <v>66</v>
+      </c>
+      <c r="R8" t="s">
+        <v>66</v>
+      </c>
+      <c r="S8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T8" t="s">
+        <v>66</v>
+      </c>
+      <c r="U8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <v>Brigade de Cavalerie de la Garde Impériale</v>
+      </c>
+      <c r="B9" t="str">
         <v>Cavalry</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C9" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="K7" t="s">
-        <v>54</v>
-      </c>
-      <c r="S7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
-        <v>Korps Reservieren</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Artillery</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Reinforcements</v>
-      </c>
-      <c r="P8" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>54</v>
-      </c>
-      <c r="R8" t="s">
-        <v>54</v>
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" t="s">
+        <v>66</v>
+      </c>
+      <c r="O9" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
